--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0004.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0004.xlsx
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Cậu cảm thấy sức mạnh trào dâng. (Thời Gian Cooldown Kỹ Năng -90%)</t>
+          <t>Cậu cảm thấy sức mạnh trào dâng. (Thời Gian hồi Kỹ Năng -90%)</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9695,7 @@
       <c r="M142" t="inlineStr">
         <is>
           <t>Chụp ảnh Zani Dodgem khiên vào kẻ địch
-Mẹo nóng từ C-MOSS: {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack 3 lần và {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack đúng lúc để tung ra Basic Attack - Đột Phá
+Mẹo nóng từ C-MOSS: {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack 3 lần và {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack đúng lúc để tung ra Basic Attack - Đột Phá
 (Các bạn có thể khám phá những cách khác để hoàn thành thử thách)</t>
         </is>
       </c>
@@ -10384,8 +10384,8 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Chụp ảnh Jiyan đeo Lưỡi Broadblade vào eo khi thực hiện Basic Attack
-Mẹo nóng từ C-MOSS: {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack 3 hoặc 4 lần để kích hoạt Stage 3 hoặc 4 của Basic Attack
+          <t>Chụp ảnh Jiyan đeo Lưỡi Đại kiếm vào eo khi thực hiện Basic Attack
+Mẹo nóng từ C-MOSS: {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack 3 hoặc 4 lần để kích hoạt Stage 3 hoặc 4 của Basic Attack
 (Cứ tự do khám phá các cách khác để hoàn thành thử thách nhé)</t>
         </is>
       </c>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Không Có Buff</t>
+          <t>Không có hiệu ứng tăng cường nào khả dụng</t>
         </is>
       </c>
     </row>
@@ -10995,7 +10995,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Mô tả kỹ năng</t>
+          <t>Mô tả Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Hướng dẫn Resonator Skill Giả</t>
+          <t>Hướng dẫn Kỹ năng Resonator</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Luyện tập Kỹ năng</t>
+          <t>Huấn Luyện Kỹ Năng</t>
         </is>
       </c>
     </row>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Tiêu hao {0}1</t>
+          <t>Tiêu thụ {0}1</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Nếu HP còn trên 80%, khi tung đòn Heavy Attack, một cơn lốc lớn sẽ xuất hiện. Kỹ năng này có Cooldown 1,5 giây.</t>
+          <t>Nếu HP còn trên 80%, khi tung đòn Heavy Attack, một cơn lốc lớn sẽ xuất hiện. Kỹ năng này có Thời gian hồi 1,5 giây.</t>
         </is>
       </c>
     </row>
@@ -22955,7 +22955,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Resonance Đầu tiên</t>
+          <t>Cộng hưởng đầu tiên</t>
         </is>
       </c>
     </row>
@@ -23085,7 +23085,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Thời gian sự kiện: Permanent</t>
+          <t>Thời gian sự kiện: Vĩnh viễn</t>
         </is>
       </c>
     </row>
@@ -23150,7 +23150,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Tất cả kẻ địch nhận &lt;color=#b72924ff&gt;5% DMG Bonus&lt;/color&gt; và bị &lt;color=#5cc96aff&gt;DEF reduced by 5%&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;5s&lt;/color&gt;, tối đa &lt;color=#b72924ff&gt;20 lần&lt;/color&gt;.</t>
+          <t>Tất cả kẻ địch nhận &lt;color=#b72924ff&gt;+5% Sát Thương&lt;/color&gt; và bị &lt;color=#5cc96aff&gt;giảm 5% DEF&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;5 giây&lt;/color&gt;, tối đa &lt;color=#b72924ff&gt;20 lần&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23215,7 +23215,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Khi bước vào trận chiến, tất cả kẻ địch nhận được Shield tương đương &lt;color=#b72924ff&gt;50% of their Max HP&lt;/color&gt;. &lt;color=#5cc96aff&gt;Casting Resonance Liberation&lt;/color&gt; sẽ trao cho tất cả Resonator trong đội Shield tương đương &lt;color=#5cc96aff&gt;10% of their Max HP&lt;/color&gt; của họ.</t>
+          <t>Khi bước vào trận chiến, tất cả kẻ địch nhận được Khiên tương đương &lt;color=#b72924ff&gt;50% HP tối đa&lt;/color&gt;. &lt;color=#5cc96aff&gt;Kích hoạt Resonance Liberation&lt;/color&gt; sẽ trao cho tất cả Resonator trong đội Khiên tương đương &lt;color=#5cc96aff&gt;10% HP tối đa&lt;/color&gt; của họ.</t>
         </is>
       </c>
     </row>
@@ -23280,7 +23280,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Murmurstown.</t>
+          <t>Kích hoạt Mạch Cộng hưởng tại Murmurstown</t>
         </is>
       </c>
     </row>
@@ -23540,7 +23540,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Valid Skill Uses: {0}</t>
+          <t>Số lần kỹ năng hợp lệ: {0}</t>
         </is>
       </c>
     </row>
@@ -23672,7 +23672,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Tăng Crit. DMG của tất cả Resonators trong đội lên 60% trong 3 giờ. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
+          <t>Tăng Crit. DMG của tất cả Resonator trong đội lên 60% trong 3 giờ. Chỉ có hiệu lực với Resonator của bạn trong Chế Độ Hợp Tác.</t>
         </is>
       </c>
     </row>
@@ -23737,7 +23737,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Giảm 50% chi phí Thể Lực khi Trèo Wall và Bơi cho tất cả Resonators trong đội trong 3 giờ. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
+          <t>Giảm 50% chi phí STA khi Trèo Tường và Bơi cho tất cả Resonator trong đội trong 3 giờ. Chỉ có hiệu lực với Resonator của bạn trong Chế Độ Hợp Tác.</t>
         </is>
       </c>
     </row>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Giảm 30% chi phí Thể Lực khi Flight cho tất cả Resonators trong đội trong 3 giờ. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
+          <t>Giảm 30% chi phí STA khi Bay cho tất cả Resonator trong đội trong 3 giờ. Chỉ có hiệu lực với Resonator của bạn trong Chế Độ Hợp Tác.</t>
         </is>
       </c>
     </row>
@@ -23867,7 +23867,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Tăng Crit. Rate cho tất cả Resonators trong đội thêm 30%, hiệu lực trong 3 giờ. Chỉ có tác dụng với Resonators của chính bạn trong Chế Độ Đồng Đội.</t>
+          <t>Tăng Crit. Rate cho tất cả Resonator trong đội thêm 30%, hiệu lực trong 3 giờ. Chỉ có tác dụng với Resonator của chính bạn trong Chế Độ Đồng Đội.</t>
         </is>
       </c>
     </row>
@@ -23932,7 +23932,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Tăng tỷ lệ rơi vật phẩm từ kẻ địch trên thế giới mở lên 50% trong 3 giờ. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
+          <t>Tăng tỷ lệ rơi vật phẩm từ kẻ địch trên thế giới mở lên 50% trong 3 giờ. Chỉ có hiệu lực với Resonator của bạn trong Chế Độ Hợp Tác.</t>
         </is>
       </c>
     </row>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Tăng tỷ lệ rơi vật phẩm từ kẻ địch trên thế giới mở lên 50% trong 3 giờ. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
+          <t>Tăng tỷ lệ rơi vật phẩm từ kẻ địch trên thế giới mở lên 50% trong 3 giờ. Chỉ có hiệu lực với Resonator của bạn trong Chế Độ Hợp Tác.</t>
         </is>
       </c>
     </row>
@@ -24062,7 +24062,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Trong giai đoạn hiện tại, mỗi cấp độ tăng Tấn Công và HP Tối Đa thêm 3.2% và Phòng Ngự thêm 0.25%.</t>
+          <t>Trong giai đoạn hiện tại, mỗi cấp độ tăng ATK và HP Tối Đa thêm 3.2% và Phòng Ngự thêm 0.25%.</t>
         </is>
       </c>
     </row>
@@ -24129,9 +24129,9 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-&lt;color=#767676&gt;A humanoid Tacet Discord with a body assembled from shattered stained glass. Glittering lights beam from its body with each move. It exudes a resilient beauty born of rebirth through destruction.
-The stained glasses that form the Vitreum Dancers are varied and unique, making each Vitreum Dancer a unique existence.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; đối với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+&lt;color=#767676&gt;Một Tacet Discord hình người, cơ thể được ghép từ những mảnh kính màu vỡ vụn. Ánh sáng lấp lánh tỏa ra từ thân thể mỗi khi di chuyển. Nó toát lên vẻ đẹp kiên cường, tái sinh từ sự hủy diệt.
+Những mảnh kính tạo nên Vitreum Dancer đều khác biệt và độc đáo, khiến mỗi cá thể Vitreum Dancer trở thành một thực thể duy nhất.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24199,10 +24199,10 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-&lt;color=#767676&gt;A humanoid Tacet Discord clad in fine attire, wielding a sharp blade and extraordinary might existing only in legends.
-Said to be the lost souls of fallen heroes, it was once witnessed slaying other Tacet Discords to protect villagers. Yet such acts were driven purely by an instinctual hunger for battle.
-Though it has lost its heart, it stubbornly clings to the vestiges of past honor, wandering the world in solitary defiance.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+&lt;color=#767676&gt;Một Tacet Discord hình người, khoác lên mình bộ lễ phục tinh tế, vung lưỡi kiếm sắc bén và sức mạnh phi thường chỉ có trong truyền thuyết.
+Tương truyền đó là linh hồn của những anh hùng đã ngã xuống, từng được chứng kiến đang tiêu diệt các Tacet Discord khác để bảo vệ dân làng. Nhưng những hành động ấy chỉ xuất phát từ bản năng thèm khát chiến đấu.
+Dù đã mất đi trái tim, nó vẫn ngoan cố bám víu vào những tàn tích danh dự xưa cũ, lang thang khắp thế gian trong sự phản kháng cô độc.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24272,12 +24272,13 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Gehinom gây Fusion DMG tương đương 4% HP tối đa của mục tiêu mỗi giây lên các mục tiêu xung quanh.
-Mỗi khi Gehinom đánh trúng mục tiêu, Cooldown chiêu của Resonance Skill và Resonance Liberation của mục tiêu sẽ bị kéo dài thêm 5 giây, kích hoạt mỗi 5 giây một lần.
-&lt;color=#767676&gt;A dragon-like Tacet Discord that haunts the peak of Penitent's End for an unknown reason, devouring all frequencies indiscriminately. Twisted by the frequencies of decay and death it consumes, it now appears as a dreadful, skeletal beast.
-Once a sacred place, this island is now a grave of sorrow, and anyone who comes for redemption must face its fire of judgment.
-Such is Gehinom, the Dragon of Dirge, whose flames burn to the bone, whose pain echoes, yearning for a final release.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; đối với &lt;color=Fire&gt;DMG Fusion&lt;/color&gt;.
+Gehinom gây DMG Fusion tương đương 4% HP tối đa của mục tiêu mỗi giây lên các mục tiêu xung quanh.
+Mỗi khi Gehinom đánh trúng mục tiêu, thời gian hồi chiêu của Resonance Skill và Resonance Liberation của mục tiêu sẽ bị kéo dài thêm 5 giây, kích hoạt mỗi 5 giây một lần.
+&lt;color=#767676&gt;Một Tacet Discord hình rồng ẩn náu trên đỉnh Penitent's End vì lý do bí ẩn, nuốt chửng mọi tần số không phân biệt.
+Bị vặn xoắn bởi những tần số của sự mục nát và cái chết mà nó hấp thụ, giờ đây nó hiện lên như một con thú khủng khiếp với bộ xương trần trụi.
+Nơi từng là thánh địa này giờ chỉ còn là nấm mồ của nỗi đau, và bất cứ ai đến để chuộc tội đều phải đối mặt với ngọn lửa phán xét của nó.
+Đó chính là Gehinom, Rồng Than Khóc, ngọn lửa của nó thiêu đốt đến tận xương, nỗi đau của nó vang vọng, khao khát được giải thoát cuối cùng.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24344,9 +24345,9 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-&lt;color=#767676&gt;Gladiators of Septimont who fight unrestrictedly, side by side with Echoes, ever in pursuit of the strong.
-Galecrest Gladiators follow the will of freedom. Bound by neither rule nor glory, they become the blade that severs all chains.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao hơn&lt;/color&gt; với &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.
+&lt;color=#767676&gt;Những chiến binh Septimont chiến đấu không giới hạn, kề vai sát cánh cùng Echo, luôn truy tìm sức mạnh đích thực.
+Chiến binh Gió Tự Do đi theo ý chí tự do. Không bị ràng buộc bởi luật lệ hay vinh quang, họ trở thành lưỡi kiếm chặt đứt mọi xiềng xích.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24413,9 +24414,9 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-&lt;color=#767676&gt;A stone statue TD that embodies deconstruction and reconstruction. Though sluggish and clumsy, its punches are devastating.
-It hurls rocks and other rock-mimic Tacet Discords as a means of attack.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.
+&lt;color=#767676&gt;Một TD tượng đá đại diện cho sự hủy diệt và tái tạo. Dù di chuyển chậm chạp và vụng về, cú đấm của nó lại vô cùng tàn khốc.
+Nó ném đá và các Tacet Discord bắt chước đá khác để tấn công.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24483,10 +24484,10 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-&lt;color=#767676&gt;A humanoid Tacet Discord clad in fine attire, wielding a sharp blade. Seen only in the pale glow of the moon.
-Said to be the lingering shadows of heroes in the old days, their kind retains a chivalrous demeanor even as they decay into TDs.
-Glorious knights who have long forgotten their titles. Protectors with nothing to defend, bound by their relentless obsession with honor.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; đối với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
+&lt;color=#767676&gt;Một Tacet Discord hình người, khoác bộ lễ phục tinh xảo, vung lưỡi kiếm sắc bén. Chúng chỉ xuất hiện dưới ánh trăng mờ ảo.
+Tương truyền là những bóng ma còn vương vấn của các anh hùng ngày xưa, dù đã hóa thành TD, chúng vẫn giữ phong thái hiệp sĩ.
+Những chiến binh vinh quang đã lãng quên danh hiệu của mình. Những người bảo vệ chẳng còn gì để bảo vệ, chỉ còn lại nỗi ám ảnh dai dẳng về danh dự.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24553,9 +24554,9 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-&lt;color=#767676&gt;Lumiscale Constructs are composed of Jué's defensive modules, commonly known as "Loong's Scales."
-Họ are found throughout the Court of Savantae ruins in Mt. Firmament, tasked with eliminating intruders and potential threats to Jué.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+&lt;color=#767676&gt;Cấu trúc Vảy Ánh Sáng được tạo thành từ các mô-đun phòng thủ của Jué, thường được gọi là "Vảy Rồng".
+Chúng xuất hiện khắp nơi trong tàn tích Court of Savantae trên núi Firmament, với nhiệm vụ tiêu diệt kẻ xâm nhập và mối đe dọa tiềm tàng đối với Jué.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24625,12 +24626,12 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-Khi bị Spectro Frazzle, Lorelei chịu thêm 100% sát thương.
-Mỗi khi Lorelei đánh trúng mục tiêu, Cooldown chiêu của Resonance Skill và Resonance Liberation của mục tiêu sẽ bị kéo dài thêm 5 giây, kích hoạt mỗi 5 giây một lần.
-&lt;color=#767676&gt;Once a remnant creature in Nimbus Sanctum, Lorelei gained intelligence through Sentinel Imperator's power, entrusted to purify corrupted frequencies drifting in the clouds.
-Yet wicked desires have transformed her into the "Queen of the Night," seeking to cloak the Sanctum in endless darkness to clear all sins.
-With her final grasp on reason, Lorelei sealed herself within the atrium, where she sings a haunting lament, awaiting one who can awaken her from this dismal slumber.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; đối với &lt;color=Dark&gt;DMG Havoc&lt;/color&gt;.
+Khi bị Spectro Frazzle, Lorelei chịu thêm 100% DMG.
+Mỗi khi Lorelei đánh trúng mục tiêu, thời gian hồi chiêu của Resonance Skill và Resonance Liberation của mục tiêu sẽ bị kéo dài thêm 5 giây, kích hoạt mỗi 5 giây một lần.
+&lt;color=#767676&gt;Từng là một sinh vật còn sót lại trong Nimbus Sanctum, Lorelei đã có được trí tuệ nhờ sức mạnh của Sentinel Imperator, được giao nhiệm vụ thanh lọc những tần số bị tha hóa trôi dạt trên mây.
+Nhưng dục vọng đen tối đã biến nàng thành "Nữ Hoàng Bóng Đêm", khao khát che phủ Sanctum trong bóng tối vĩnh cửu để xóa sạch mọi tội lỗi.
+Với chút lý trí cuối cùng, Lorelei đã tự giam mình trong đại sảnh, nơi nàng cất lên khúc bi ca ám ảnh, chờ đợi ai đó có thể đánh thức mình khỏi giấc ngủ u tối này.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24697,9 +24698,9 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-&lt;color=#767676&gt;Gladiators of Septimont who fight unrestrictedly, side by side with Echoes, ever in pursuit of the strong.
-Flamecrest Gladiators embody a warrior's undying passion. Wounds become fire, hardship their forge. Battle after battle, they chase a blood-lit path to their truest form.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+&lt;color=#767676&gt;Những đấu sĩ của Septimont chiến đấu không giới hạn, sát cánh cùng Echo, luôn theo đuổi sức mạnh.
+Flamecrest Gladiators mang trong mình ngọn lửa đam mê bất diệt của chiến binh. Vết thương hóa thành lửa, gian khổ là lò rèn. Trận chiến nối tiếp trận chiến, họ theo đuổi con đường thấm đẫm máu để tìm về hình hài chân thật nhất.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24767,10 +24768,10 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-&lt;color=#767676&gt;A humanoid Tacet Discord clad in fine attire, wielding a sharp blade. Seen only in the radiance of the sun.
-Said to be the lost souls of fallen heroes, it retains an air of commanding dignity, even as a Tacet Discord.
-Once a knight who has long forgotten the title they once bore, it has lost all it was sworn to protect. Now, only an unyielding obsession with honor remains.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; đối với &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.
+&lt;color=#767676&gt;Một Tacet Discord hình người, khoác bộ lễ phục tinh xảo, vung lưỡi kiếm sắc bén. Chúng chỉ xuất hiện dưới ánh mặt trời rực rỡ.
+Tương truyền là linh hồn lạc lõng của những anh hùng đã ngã xuống, dù hóa thành Tacet Discord, chúng vẫn toát lên vẻ uy nghiêm của bậc thống lĩnh.
+Từng là một hiệp sĩ đã quên mất danh hiệu mình từng mang, chúng đã mất tất cả những gì từng thề bảo vệ. Giờ đây, chỉ còn lại nỗi ám ảnh không thể buông bỏ về danh dự.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24837,9 +24838,9 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-&lt;color=#767676&gt;An enormous feline-mimic TD, only sighted in Mt. Firmament in Huanglong.
-According to the Hongzhen Chronicle, it is a solitary TD with four claws and a scaly back. It is called "Lightcrusher" because of the glowing tracks left in its wake.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.
+&lt;color=#767676&gt;Một TD bắt chước loài mèo khổng lồ, chỉ được phát hiện tại Mt. Firmament ở Huanglong.
+Theo Hồng Chân Lục, đây là một TD đơn độc với bốn móng vuốt và lưng phủ vảy. Nó được gọi là "Lightcrusher" vì những vệt sáng rực rỡ để lại trên đường đi.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24906,9 +24907,9 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-&lt;color=#767676&gt;Kerasaurs are fierce, amphibious Tacet Discords mimicking Saurosuchus. Họ gain their name from the spiky scales covering their bodies. Kerasaurs are not indigenous to Septimont. Họ were introduced as gladiatorial opponents in matches for their distinct appearance and aggressive behavior.
-Their pronounced territorial instincts also make them the ideal Echoes to serve in the city's defense force once tamed.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao hơn&lt;/color&gt; với &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.
+&lt;color=#767676&gt;Kerasaurs là những Tacet Discord lưỡng cư bắt chước loài Saurosuchus. Chúng được đặt tên theo lớp vảy gai nhọn bao phủ cơ thể. Kerasaurs không phải loài bản địa của Septimont. Chúng được đưa vào làm đối thủ trong các trận đấu vì ngoại hình đặc biệt và tính hung hãn.
+Bản năng lãnh thổ mạnh mẽ cũng khiến chúng trở thành Echo lý tưởng để phục vụ trong lực lượng phòng thủ thành phố sau khi được thuần hóa.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24979,13 +24980,13 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+          <t>Kẻ địch có &lt;color=HighlightB&gt;Kháng cao hơn&lt;/color&gt; đối với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
 Khi Arsinosa tấn công mục tiêu, STA của mục tiêu sẽ bị giảm 100%, kích hoạt mỗi 10 giây một lần.
-Khi bước vào trận chiến, Arsinosa nhận được một Lớp Shield bằng 20% HP tối đa của cô. Nếu không chịu sát thương trong hơn 10 giây, cô sẽ nhận thêm một Lớp Shield bằng 20% HP tối đa.
-Khi Arsinosa tấn công mục tiêu, Cooldown chiêu của Resonance Skill và Resonance Liberation của mục tiêu sẽ bị kéo dài thêm 5 giây, kích hoạt mỗi 5 giây một lần.
-&lt;color=#767676&gt;Cô ấy guards the City of Glory, a valiant lioness of the arena.
-Built with the pristine white stones that Gryphons are carved out of and tempered in the echoes of battle cries and the laughter of heroes.
-This is Arsinosa, ever steadfast, watching over Septimont’s glory for all time.&lt;/color&gt;</t>
+Khi bước vào trận chiến, Arsinosa nhận được một Lớp Khiên bằng 20% HP tối đa của cô. Nếu không chịu DMG trong hơn 10 giây, cô sẽ nhận thêm một Lớp Khiên bằng 20% HP tối đa.
+Khi Arsinosa tấn công mục tiêu, thời gian hồi chiêu của Resonance Skill và Resonance Liberation của mục tiêu sẽ bị kéo dài thêm 5 giây, kích hoạt mỗi 5 giây một lần.
+&lt;color=#767676&gt;Nữ sư tử dũng mãnh của đấu trường, bảo vệ Thành Phố Vinh Quang.
+Được xây dựng từ những viên đá trắng tinh khiết như tượng Gryphon và tôi luyện trong tiếng vang chiến trận cùng tiếng cười của những anh hùng.
+Đây là Arsinosa, luôn kiên định, canh giữ vinh quang của Septimont mãi mãi.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25054,11 +25055,11 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-Khi Lampylumen Myriad gây sát thương, nó sẽ áp đặt 3 tầng hiệu ứng Glacio Chafe lên mục tiêu, kích hoạt mỗi 6 giây.
-&lt;color=#767676&gt;An ensnarer that slumbers in a freezing mine pit, obsessed with collecting and imitating sounds. It can imitate human speech through a vibrating hum.
-Lampylumen Myriad uses sound as bait to lure its prey, which will be frozen in the deep cold. The loss of warmth and the illusion before dying will cause human beings to pour out their last words, which contain great emotional fluctuations.
-For Lampylumen Myriad, this is the frequency of the supreme taste.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;Kháng cao hơn&lt;/color&gt; đối với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+Khi Lampylumen Myriad gây DMG, nó sẽ áp đặt 3 tầng hiệu ứng Glacio Chafe lên mục tiêu, kích hoạt mỗi 6 giây.
+&lt;color=#767676&gt;Một kẻ phục kích ngủ quên trong hầm mỏ băng giá, ám ảnh với việc thu thập và bắt chước âm thanh. Nó có thể bắt chước giọng nói con người qua tiếng rung vo ve.
+Lampylumen Myriad dùng âm thanh làm mồi nhử con mồi, rồi đóng băng chúng trong cái lạnh thấu xương. Sự mất đi hơi ấm và ảo giác trước khi chết khiến con người thốt ra những lời cuối cùng chứa đầy cảm xúc mãnh liệt.
+Với Lampylumen Myriad, đây chính là tần số của hương vị tuyệt hảo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25125,9 +25126,9 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-&lt;color=#767676&gt;Gladiators of Septimont who fight unrestrictedly, side by side with Echoes, ever in pursuit of the strong.
-Lightcrest Gladiators uphold the ideal of justice. Họ bow to no tyrant, yield to no shadow. If justice has rotted, they shall forge it anew in light.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.
+&lt;color=#767676&gt;Những chiến binh Septimont không bị ràng buộc, chiến đấu bên cạnh Echo, luôn truy tìm kẻ mạnh.
+Gladiator Ánh Sáng theo đuổi lý tưởng công lý. Họ không cúi đầu trước bạo chúa, không khuất phục trước bóng tối. Nếu công lý đã mục rữa, họ sẽ rèn lại nó trong ánh sáng.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25194,9 +25195,9 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-&lt;color=#767676&gt;Gladiators of Septimont who fight unrestrictedly, side by side with Echoes, ever in pursuit of the strong.
-Frostcrest Gladiators bear unyielding resolve. Their fortitude is impervious to frost and bitter cold. Though blades may shatter, their creed endures.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+&lt;color=#767676&gt;Những đấu sĩ của Septimont chiến đấu không giới hạn, sát cánh cùng Echo, luôn theo đuổi sức mạnh.
+Frostcrest Gladiators mang trong mình ý chí bất khuất. Sự kiên cường của họ không gì lay chuyển được, dù băng giá hay cái lạnh thấu xương. Dù lưỡi kiếm có vỡ tan, tín niệm của họ vẫn trường tồn.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25266,12 +25267,12 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-Tấn công phản đòn Kelpie sẽ làm giảm thêm 50% Concerto Vibrancy của nó.
+          <t>Kẻ địch có &lt;color=HighlightB&gt;Kháng cao hơn&lt;/color&gt; đối với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.
+Tấn công phản đòn Kelpie sẽ làm giảm thêm 50% Sức Mạnh Rung Động của nó.
 Khi Kelpie không bị Hóa Đá, toàn bộ Kháng thuộc tính của nó tăng 200%.
-Khi Kelpie tấn công mục tiêu, Cooldown chiêu của Resonance Skill và Resonance Liberation của mục tiêu sẽ bị kéo dài thêm 5 giây, kích hoạt mỗi 5 giây một lần.
-&lt;color=#767676&gt;A humanoid TD born from the deep sea. Commonly found in all types of waters, it's known for its aggression and ferocity.
-It attacks with sharp claws laced with paralytic toxins, then rips its prey apart and swallows them whole.&lt;/color&gt;</t>
+Khi Kelpie tấn công mục tiêu, thời gian hồi chiêu của Resonance Skill và Resonance Liberation của mục tiêu sẽ bị kéo dài thêm 5 giây, kích hoạt mỗi 5 giây một lần.
+&lt;color=#767676&gt;Một Tacet Discord hình người sinh ra từ biển sâu. Thường xuất hiện ở mọi loại vùng nước, nổi tiếng với sự hung hãn và tàn bạo.
+Nó tấn công bằng móng vuốt sắc bén tẩm độc gây tê liệt, rồi xé xác con mồi và nuốt chửng toàn bộ.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25337,8 +25338,8 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-&lt;color=#767676&gt;A ferocious bear-mimic TD with Tacetite spikes on its head, neck, and shoulders. Its swings strike like a hurricane.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.
+&lt;color=#767676&gt;Một Tacet Discord bắt chước loài gấu hung dữ, với những gai Tacetite nhọn trên đầu, cổ và vai. Những cú vung tay của nó mạnh như bão tố.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25405,9 +25406,9 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-&lt;color=#767676&gt;Gladiators of Septimont who fight unrestrictedly, side by side with Echoes, ever in pursuit of the strong.
-Thundercrest Gladiators wield stormborne might. Unmoved by favor and unbowed by power. Beneath the thunder’s judgment, right and wrong divide.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao hơn&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+&lt;color=#767676&gt;Những chiến binh Septimont chiến đấu không giới hạn, kề vai sát cánh cùng Echo, luôn truy tìm sức mạnh đích thực.
+Chiến binh Sấm Sét vận dụng sức mạnh của bão tố. Không bị lung lay bởi ân huệ, không cúi đầu trước quyền lực. Dưới sự phán xét của sấm sét, đúng sai phân minh.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25474,9 +25475,9 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-&lt;color=#767676&gt;It holds the authority to command other Echoes of the Order, carrying out the Order's will to eliminate any transgressors.
-Just as the Order's authority is inviolable, so too is the power of the Echo.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.
+&lt;color=#767676&gt;Nó nắm quyền chỉ huy các Echo khác của Order, thực thi ý chí của Order để tiêu diệt mọi kẻ vi phạm.
+Giống như quyền uy của Order bất khả xâm phạm, sức mạnh của Echo cũng vậy.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25544,10 +25545,10 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- Each time you deploy an Echo, increase one of your Echoes' STR and CON by {2}.&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu trúc một lá bài, họ không nhận được Năng Lượng.
+- Mỗi khi triển khai một Echo, tăng {2} STR và CON cho một trong các Echo của bạn.&lt;/color&gt;
 - Nạp Năng: Lá bài này nhận 1 điểm Nạp Năng mỗi khi bạn Tái Cấu trúc một lá bài.
-- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và tăng {1} STR và CON cho tất cả Echoes của bạn trong 1 lượt.</t>
+- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và tăng {1} STR và CON cho tất cả Echo của bạn trong 1 lượt.</t>
         </is>
       </c>
     </row>
@@ -25616,11 +25617,11 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- When the Battle Stage starts, increase all your Echoes' STR and CON by {3}.
-- Each time you deploy an Echo, increase one of your Echoes' STR and CON by {2}.&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu Trúc thẻ, họ không nhận được Năng Lượng.
+- Khi Giai Đoạn Chiến Đấu bắt đầu, tăng toàn bộ chỉ số Sức Mạnh và Thể Trạng của Cộng Hưởng Giả của ngươi thêm {3}.
+- Mỗi lần triển khai Cộng Hưởng Giả, tăng chỉ số Sức Mạnh và Thể Trạng của một Cộng Hưởng Giả của ngươi thêm {2}.&lt;/color&gt;
 - Nạp Năng: Thẻ này nhận 1 điểm Nạp Năng mỗi khi ngươi Tái Cấu Trúc thẻ.
-- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và tăng chỉ số Sức Mạnh và Thể Trạng của tất cả Resonator của ngươi thêm {1} trong 1 hiệp.</t>
+- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và tăng chỉ số Sức Mạnh và Thể Trạng của tất cả Cộng Hưởng Giả của ngươi thêm {1} trong 1 hiệp.</t>
         </is>
       </c>
     </row>
@@ -25690,12 +25691,12 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- When the Battle Stage starts, increase all your Echoes' STR and CON by {3}.
-- When the round starts, you recover {4} HP.
-- Each time you deploy an Echo, increase one of your Echoes' STR and CON by {2}.&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu Trúc thẻ, họ không nhận được Năng Lượng.
+- Khi Giai Đoạn Chiến Đấu bắt đầu, tăng toàn bộ chỉ số Sức Mạnh và Thể Trạng của Cộng Hưởng Giả của ngươi thêm {3}.
+- Khi hiệp bắt đầu, ngươi hồi {4} HP.
+- Mỗi lần triển khai Cộng Hưởng Giả, tăng chỉ số Sức Mạnh và Thể Trạng của một Cộng Hưởng Giả của ngươi thêm {2}.&lt;/color&gt;
 - Nạp Năng: Thẻ này nhận 1 điểm Nạp Năng mỗi khi ngươi Tái Cấu Trúc thẻ.
-- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và tăng chỉ số Sức Mạnh và Thể Trạng của tất cả Resonator của ngươi thêm {1} trong 1 hiệp.</t>
+- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và tăng chỉ số Sức Mạnh và Thể Trạng của tất cả Cộng Hưởng Giả của ngươi thêm {1} trong 1 hiệp.</t>
         </is>
       </c>
     </row>
@@ -25764,7 +25765,7 @@
         <is>
           <t>- Khi bắt đầu trận đấu, nếu bộ bài của bạn có ít nhất 6 lá Aero, nhận các hiệu ứng sau:
 - Nạp Năng: Lá bài này nhận 1 tầng Nạp Năng mỗi khi bạn Tái Cấu Trúc một lá bài.
-- Quá Tải: Khi Nạp Năng đạt {0} tầng, xóa toàn bộ tầng và tăng STR và CON của tất cả Echoes của bạn lên {1} trong 1 lượt.</t>
+- Quá Tải: Khi Nạp Năng đạt {0} tầng, xóa toàn bộ tầng và tăng STR và CON của tất cả Echo của bạn lên {1} trong 1 lượt.</t>
         </is>
       </c>
     </row>
@@ -25829,7 +25830,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Mỗi khi đối thủ triển khai một Echo, Resonator sẽ mất 5 HP.</t>
+          <t>Mỗi khi đối thủ triển khai một Echo, Cộng Hưởng Giả sẽ mất 5 HP.</t>
         </is>
       </c>
     </row>
@@ -25894,7 +25895,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Mỗi lần Resonator chịu sát thương sẽ được giảm đi 5.</t>
+          <t>Mỗi lần Cộng Hưởng Giả chịu DMG sẽ được giảm đi 5.</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25960,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Mỗi khi đối thủ triển khai một thẻ bài, Resonator sẽ mất 66 HP.</t>
+          <t>Mỗi khi đối thủ triển khai một thẻ bài, Cộng Hưởng Giả sẽ mất 66 HP.</t>
         </is>
       </c>
     </row>
@@ -26154,7 +26155,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Mỗi khi đối thủ triển khai một thẻ Novelty, Resonator sẽ mất 10 HP.</t>
+          <t>Mỗi khi đối thủ triển khai một thẻ Novelty, Cộng Hưởng Giả sẽ mất 10 HP.</t>
         </is>
       </c>
     </row>
@@ -26219,7 +26220,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Mỗi khi đối thủ triển khai một Echo, Resonator sẽ mất 5 HP.</t>
+          <t>Mỗi khi đối thủ triển khai một Echo, Cộng Hưởng Giả sẽ mất 5 HP.</t>
         </is>
       </c>
     </row>
@@ -26284,7 +26285,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Mỗi lần Resonator chịu sát thương sẽ được giảm đi 5.</t>
+          <t>Mỗi lần Cộng Hưởng Giả chịu DMG sẽ được giảm đi 5.</t>
         </is>
       </c>
     </row>
@@ -26349,7 +26350,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Mỗi khi đối thủ triển khai một thẻ bài, Resonator sẽ mất 66 HP.</t>
+          <t>Mỗi khi đối thủ triển khai một thẻ bài, Cộng Hưởng Giả sẽ mất 66 HP.</t>
         </is>
       </c>
     </row>
@@ -26544,7 +26545,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Mỗi khi đối thủ triển khai một thẻ Novelty, Resonator sẽ mất 10 HP.</t>
+          <t>Mỗi khi đối thủ triển khai một thẻ Novelty, Cộng Hưởng Giả sẽ mất 10 HP.</t>
         </is>
       </c>
     </row>
@@ -26674,7 +26675,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Số lần sử dụng Active Skill của The Novelty. Sau khi sử dụng hết số lần, The Novelty sẽ được trả về bộ bài.</t>
+          <t>Số lần sử dụng Kỹ Năng Chủ Động của The Novelty. Sau khi sử dụng hết số lần, The Novelty sẽ được trả về bộ bài.</t>
         </is>
       </c>
     </row>
@@ -26804,7 +26805,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Skill Đặc Biệt chỉ có thể sử dụng một lần mỗi lượt. Tuy nhiên, một số thẻ có hiệu ứng Đặt lại có thể khôi phục số lần sử dụng Active Skill của thẻ.</t>
+          <t>Kỹ năng Đặc Biệt chỉ có thể sử dụng một lần mỗi lượt. Tuy nhiên, một số thẻ có hiệu ứng Reset có thể khôi phục số lần sử dụng Kỹ Năng Chủ Động của thẻ.</t>
         </is>
       </c>
     </row>
@@ -26934,7 +26935,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Tính Năng Mới: Thời Hạn</t>
+          <t>Mới Lạ: Thời Hạn</t>
         </is>
       </c>
     </row>
@@ -26999,7 +27000,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Thử thách: Sử dụng Skill Chủ động 5 lần (Progress: {0}), hoặc đạt Round 5.</t>
+          <t>Thử thách: Sử dụng Kỹ năng Chủ động 5 lần (Tiến độ: {0}), hoặc đạt Vòng 5.</t>
         </is>
       </c>
     </row>
@@ -27064,7 +27065,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Thử thách: Sử dụng Skill Chủ động 5 lần (Progress: {0}), hoặc đạt Round 5.</t>
+          <t>Thử thách: Sử dụng Kỹ năng Chủ động 5 lần (Tiến độ: {0}), hoặc đạt Vòng 5.</t>
         </is>
       </c>
     </row>
@@ -27129,7 +27130,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Thử thách: Trigger hiệu ứng Nạp năng lượng 5 lần (Progress: {0}), hoặc đạt Round 5.</t>
+          <t>Thử thách: Kích hoạt hiệu ứng Nạp năng lượng 5 lần (Tiến độ: {0}), hoặc đạt Vòng 5.</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27195,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Chiến Thuật Chủ Động ({0}): Trong lượt này, tăng sức mạnh của Echoes lên {1}.</t>
+          <t>Chiến Thuật Chủ Động ({0}): Trong lượt này, tăng sức mạnh của Echo lên {1}.</t>
         </is>
       </c>
     </row>
@@ -27259,7 +27260,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Passive Tactic: Mỗi lần Điều Tần, ngẫu nhiên tăng {0} STR cho một Echoes của bạn đến hết hiệp.</t>
+          <t>Thụ Động Chiến Thuật: Mỗi lần Điều Tần, ngẫu nhiên tăng {0} STR cho một Echo của bạn đến hết hiệp.</t>
         </is>
       </c>
     </row>
@@ -27325,7 +27326,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Là một Roya, Lana đặc biệt hứng thú với những chiếc mô tô thám hiểm của Startorch Academy. Một tin đồn nào đó đã khiến cô nảy ra một ý tưởng khá điên rồ…
+          <t>Là một Roya, Lana đặc biệt hứng thú với những chiếc mô tô thám hiểm của Học viện Startorch. Một tin đồn nào đó đã khiến cô nảy ra một ý tưởng khá điên rồ…
 Đặc tính Võ sĩ: Võ sĩ sẽ mất 5 HP mỗi khi đối thủ triển khai Echo.</t>
         </is>
       </c>
@@ -27393,7 +27394,7 @@
       <c r="M411" t="inlineStr">
         <is>
           <t>Joanna hiện đang phụ trách thu thập dữ liệu ở Roya Frostlands. Công việc nhàm chán đến phát ngán, cô ấy đang rất cần một đối thủ mạnh để giết thời gian.
-Đặc tính Đấu Thủ: Mỗi lần nhận sát thương, Đấu Thủ sẽ giảm 5 sát thương nhận vào.</t>
+Đặc tính Đấu Thủ: Mỗi lần nhận DMG, Đấu Thủ sẽ giảm 5 DMG nhận vào.</t>
         </is>
       </c>
     </row>
@@ -27726,7 +27727,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Increase HP Cơ Bản lên 45. Khi bắt đầu Giai Đoạn Triển Khai, rút thêm 2 lá bài.</t>
+          <t>Tăng HP Cơ Bản lên 45. Khi bắt đầu Giai Đoạn Triển Khai, rút thêm 2 lá bài.</t>
         </is>
       </c>
     </row>
@@ -27791,7 +27792,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Increase HP Cơ Bản lên 50. Ở đầu hiệp đầu tiên, rút 8 lá bài tùy chọn và nhận thêm 6 Năng Lượng.</t>
+          <t>Tăng HP Cơ Bản lên 50. Ở đầu hiệp đầu tiên, rút 8 lá bài tùy chọn và nhận thêm 6 Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -27856,7 +27857,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Increase HP Cơ Bản lên 55. Brant chịu ít hơn 6 sát thương mỗi hiệp trong Battle Stage.</t>
+          <t>Tăng HP Cơ Bản lên 55. Brant chịu ít hơn 6 sát thương mỗi hiệp trong Giai Đoạn Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -27921,7 +27922,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Increase HP Cơ Bản lên 55. Trong 5 hiệp đầu, STR và CON của Echoes của Ciaccona tăng thêm 2.</t>
+          <t>Tăng HP Cơ Bản lên 55. Trong 5 hiệp đầu, STR và CON của Echo của Ciaccona tăng thêm 2.</t>
         </is>
       </c>
     </row>
@@ -27986,7 +27987,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Increase HP Cơ Bản lên 55. Lupa rút thêm 3 lá bài trong mỗi lượt triển khai ở Giai Đoạn Triển Khai.</t>
+          <t>Tăng HP Cơ Bản lên 55. Lupa rút thêm 3 lá bài trong mỗi lượt triển khai ở Giai Đoạn Triển Khai.</t>
         </is>
       </c>
     </row>
@@ -28051,7 +28052,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Increase HP Cơ Bản lên 55. STR của Core Echo của Calcharo tăng thêm 4 và CON tăng thêm 8.</t>
+          <t>Tăng HP Cơ Bản lên 55. STR của Core Echo của Calcharo tăng thêm 4 và CON tăng thêm 8.</t>
         </is>
       </c>
     </row>
@@ -28116,7 +28117,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Increase HP Cơ Bản lên 45. Khi bắt đầu Giai Đoạn Triển Khai, Cao Thủ Duel Sĩ rút thêm 1 lá bài. Trong trận đấu này, STR và CON của Echoes của Cao Thủ Duel Sĩ tăng thêm 2.</t>
+          <t>Tăng HP Cơ Bản lên 45. Khi bắt đầu Giai Đoạn Triển Khai, Cao Thủ Đấu Sĩ rút thêm 1 lá bài. Trong trận đấu này, STR và CON của Echo của Cao Thủ Đấu Sĩ tăng thêm 2.</t>
         </is>
       </c>
     </row>
@@ -28181,7 +28182,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Mỗi khi đối thủ triển khai một Echo, Resonator sẽ mất 5 HP.</t>
+          <t>Mỗi khi đối thủ triển khai một Echo, Cộng Hưởng Giả sẽ mất 5 HP.</t>
         </is>
       </c>
     </row>
@@ -28246,7 +28247,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Mỗi lần Resonator chịu sát thương sẽ được giảm đi 5.</t>
+          <t>Mỗi lần Cộng Hưởng Giả chịu DMG sẽ được giảm đi 5.</t>
         </is>
       </c>
     </row>
@@ -28311,7 +28312,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Mỗi khi đối thủ triển khai một thẻ bài, Resonator sẽ mất 66 HP.</t>
+          <t>Mỗi khi đối thủ triển khai một thẻ bài, Cộng Hưởng Giả sẽ mất 66 HP.</t>
         </is>
       </c>
     </row>
@@ -28506,7 +28507,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Mỗi khi đối thủ triển khai một thẻ Novelty, Resonator sẽ mất 10 HP.</t>
+          <t>Mỗi khi đối thủ triển khai một thẻ Novelty, Cộng Hưởng Giả sẽ mất 10 HP.</t>
         </is>
       </c>
     </row>
@@ -28571,7 +28572,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Kỹ năng Slow Motion đang Cooldown. Không thể sử dụng lúc này.</t>
+          <t>Kỹ năng Slow Motion đang hồi chiêu. Không thể sử dụng lúc này.</t>
         </is>
       </c>
     </row>
@@ -28899,8 +28900,8 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Khi Thủy Triều High đến gần, một tai họa tiềm ẩn đang thức tỉnh, ánh mắt hắn đổ dồn về biên giới Septimont. Ephor Augusta mời ngươi đến Sanguis Plateaus để tham gia một cuộc săn định mệnh, cuộc săn có thể quyết định sự sống còn của vương quốc. Để lấy lại di vật thất lạc của Sentinel Imperator và ngăn chặn Dark Tide trước khi nó nuốt chửng Rinascita một lần nữa, ngươi cùng các Chiến Binh Septimont lên đường thám hiểm...
-Nhưng trên vùng đất hoang dã khắc nghiệt của Sanguis Plateaus, ranh giới giữa kẻ săn mồi và con mồi mong manh như sợi tóc. Ai mới thực sự nắm giữ vận mệnh? Và ai sẽ vươn lên đội vương miện vinh quang? Chỉ kẻ chiến thắng mới có quyền trả lời.</t>
+          <t>Khi Thủy Triều Cao đến gần, một tai họa tiềm ẩn đang thức tỉnh, ánh mắt hắn đổ dồn về biên giới Septimont. Ephor Augusta mời ngươi đến Cao Nguyên Sanguis để tham gia một cuộc săn định mệnh, cuộc săn có thể quyết định sự sống còn của vương quốc. Để lấy lại di vật thất lạc của Sentinel Imperator và ngăn chặn Dark Tide trước khi nó nuốt chửng Rinascita một lần nữa, ngươi cùng các Chiến Binh Septimont lên đường thám hiểm...
+Nhưng trên vùng đất hoang dã khắc nghiệt của Cao Nguyên Sanguis, ranh giới giữa kẻ săn mồi và con mồi mong manh như sợi tóc. Ai mới thực sự nắm giữ vận mệnh? Và ai sẽ vươn lên đội vương miện vinh quang? Chỉ kẻ chiến thắng mới có quyền trả lời.</t>
         </is>
       </c>
     </row>
@@ -28965,7 +28966,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Triệu hồi &lt;color=#c49e55&gt;&lt;te href=800018&gt;Breeze Breaker&lt;/te&gt;&lt;/color&gt;, gây Aero DMG lên kẻ địch xung quanh. Trong thời gian ngắn, Movement Speed tăng lên, và Resonator nhận thêm Sát Thương dựa trên phần thưởng Movement Speed.</t>
+          <t>Triệu hồi &lt;color=#c49e55&gt;&lt;te href=800018&gt;Breeze Breaker&lt;/te&gt;&lt;/color&gt;, gây Sát Thương Aero lên kẻ địch xung quanh. Trong thời gian ngắn, Tốc Độ Di Chuyển tăng lên, và Resonator nhận thêm Sát Thương dựa trên phần thưởng Tốc Độ Di Chuyển.</t>
         </is>
       </c>
     </row>
@@ -29030,7 +29031,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Hiệu ứng của Active Skill &lt;color=#c49e55&gt;&lt;te href=800018&gt;Breeze Breaker&lt;/te&gt;&lt;/color&gt; được tăng cường.</t>
+          <t>Hiệu ứng của Kỹ Năng Chủ Động &lt;color=#c49e55&gt;&lt;te href=800018&gt;Breeze Breaker&lt;/te&gt;&lt;/color&gt; được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -29095,7 +29096,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Hiệu ứng của Active Skill &lt;color=#c49e55&gt;&lt;te href=800018&gt;Breeze Breaker&lt;/te&gt;&lt;/color&gt; được tăng cường thêm.</t>
+          <t>Hiệu ứng của Kỹ Năng Chủ Động &lt;color=#c49e55&gt;&lt;te href=800018&gt;Breeze Breaker&lt;/te&gt;&lt;/color&gt; được tăng cường thêm.</t>
         </is>
       </c>
     </row>
@@ -29160,7 +29161,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Triệu hồi &lt;color=#c49e55&gt;&lt;te href=800019&gt;Ashen Oath&lt;/te&gt;&lt;/color&gt;, gây Fusion DMG lên kẻ địch xung quanh, tăng Crit. Rate và Attack Speed của Galbrena trong thời gian ngắn.</t>
+          <t>Triệu hồi &lt;color=#c49e55&gt;&lt;te href=800019&gt;Ashen Oath&lt;/te&gt;&lt;/color&gt;, gây Sát Thương Fusion lên kẻ địch xung quanh, tăng Crit. Rate và Tốc Độ Tấn Công của Galbrena trong thời gian ngắn.</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29226,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Hiệu ứng của Active Skill &lt;color=#c49e55&gt;&lt;te href=800019&gt;Ashen Oath&lt;/te&gt;&lt;/color&gt; được tăng cường.</t>
+          <t>Hiệu ứng của Kỹ Năng Chủ Động &lt;color=#c49e55&gt;&lt;te href=800019&gt;Ashen Oath&lt;/te&gt;&lt;/color&gt; được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -29290,7 +29291,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Hiệu ứng của Active Skill &lt;color=#c49e55&gt;&lt;te href=800019&gt;Ashen Oath&lt;/te&gt;&lt;/color&gt; được tăng cường thêm.</t>
+          <t>Hiệu ứng của Kỹ Năng Chủ Động &lt;color=#c49e55&gt;&lt;te href=800019&gt;Ashen Oath&lt;/te&gt;&lt;/color&gt; được tăng cường thêm.</t>
         </is>
       </c>
     </row>
@@ -29355,7 +29356,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=#c49e55&gt;&lt;te href=800020&gt;Waxing Moon&lt;/te&gt;&lt;/color&gt;, gây Aero DMG cho kẻ địch xung quanh và tiêu hao HP. Trong thời gian ngắn, một tỷ lệ lớn HP sẽ được chuyển hóa thành Tấn Công.</t>
+          <t>Kích hoạt &lt;color=#c49e55&gt;&lt;te href=800020&gt;Trăng Tròn Dần&lt;/te&gt;&lt;/color&gt;, gây Sát Thương Aero cho kẻ địch xung quanh và tiêu hao HP. Trong thời gian ngắn, một tỷ lệ lớn HP sẽ được chuyển hóa thành ATK.</t>
         </is>
       </c>
     </row>
@@ -29420,7 +29421,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Hiệu ứng của Active Skill &lt;color=#c49e55&gt;&lt;te href=800020&gt;Waxing Moon&lt;/te&gt;&lt;/color&gt; được tăng cường.</t>
+          <t>Hiệu ứng của Kỹ Năng Chủ Động &lt;color=#c49e55&gt;&lt;te href=800020&gt;Waxing Moon&lt;/te&gt;&lt;/color&gt; được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -29485,7 +29486,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Hiệu ứng của Active Skill &lt;color=#c49e55&gt;&lt;te href=800020&gt;Waxing Moon&lt;/te&gt;&lt;/color&gt; được tăng cường thêm.</t>
+          <t>Hiệu ứng của Kỹ Năng Chủ Động &lt;color=#c49e55&gt;&lt;te href=800020&gt;Waxing Moon&lt;/te&gt;&lt;/color&gt; được tăng cường thêm.</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29681,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Kích hoạt Mạch Resonance tại Central Plains</t>
+          <t>Kích hoạt Mạch Cộng Hưởng tại Central Plains</t>
         </is>
       </c>
     </row>
@@ -29745,7 +29746,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Kích hoạt Mạch Resonance tại Port City of Guixu</t>
+          <t>Kích hoạt Mạch Cộng Hưởng tại Thành Phố Cảng Guixu</t>
         </is>
       </c>
     </row>
@@ -29810,7 +29811,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Kích hoạt 6 Resonance Beacon</t>
+          <t>Kích hoạt 6 Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -29875,7 +29876,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Kích hoạt Mạch Resonance tại Tiger's Maw</t>
+          <t>Kích hoạt Mạch Cộng Hưởng tại Hàm Hổ</t>
         </is>
       </c>
     </row>
@@ -29940,7 +29941,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Hoàn thành Hướng dẫn Resonator Skill Giả 2 lần</t>
+          <t>Hoàn thành Hướng dẫn Kỹ năng Resonator 2 lần</t>
         </is>
       </c>
     </row>
@@ -30005,7 +30006,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Kích hoạt Mạch Resonance tại Rừng U Tối</t>
+          <t>Kích hoạt Mạch Cộng Hưởng tại Rừng U Tối</t>
         </is>
       </c>
     </row>
@@ -30200,7 +30201,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>HEAVY ATTACK</t>
+          <t>ĐÒN TẤN CÔNG MẠNH</t>
         </is>
       </c>
     </row>
@@ -30265,7 +30266,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>RESONANCE SKILL</t>
+          <t>KỸ NĂNG CỘNG HƯỞNG</t>
         </is>
       </c>
     </row>
@@ -30330,7 +30331,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>RESONANCE BEACON</t>
+          <t>ĐIỂM CỘNG HƯỞNG</t>
         </is>
       </c>
     </row>
@@ -30395,7 +30396,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>RESONANCE LIBERATION</t>
+          <t>GIẢI PHÓNG CỘNG HƯỞNG</t>
         </is>
       </c>
     </row>
@@ -30460,7 +30461,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>RESONANCE ENERGY</t>
+          <t>NĂNG LƯỢNG CỘNG HƯỞNG</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30591,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>CONCERTO SKILL</t>
+          <t>KỸ NĂNG CONCERTO</t>
         </is>
       </c>
     </row>
@@ -30720,7 +30721,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Khôi phục tất cả thông điệp ẩn trong sự kiện "Search nào! Những mảnh vỡ của Lahai-Roi."</t>
+          <t>Khôi phục tất cả thông điệp ẩn trong sự kiện "Tìm kiếm nào! Những mảnh vỡ của Lahai-Roi."</t>
         </is>
       </c>
     </row>
@@ -30785,7 +30786,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Data thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa hàng Simulation Training.</t>
+          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Dữ Liệu thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa Hàng Huấn Luyện Mô Phỏng.</t>
         </is>
       </c>
     </row>
@@ -30850,7 +30851,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Data thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa hàng Simulation Training.</t>
+          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Dữ Liệu thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa Hàng Huấn Luyện Mô Phỏng.</t>
         </is>
       </c>
     </row>
@@ -30915,7 +30916,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Data thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa hàng Simulation Training.</t>
+          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Dữ Liệu thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa Hàng Huấn Luyện Mô Phỏng.</t>
         </is>
       </c>
     </row>
@@ -30980,7 +30981,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Data thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa hàng Simulation Training.</t>
+          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Dữ Liệu thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa Hàng Huấn Luyện Mô Phỏng.</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31046,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>[Kháng Cự]: Kẻ địch này có &lt;color=Ice&gt;Glacio RES&lt;/color&gt; cao hơn.</t>
+          <t>[Kháng Cự]: Kẻ địch này có &lt;color=Ice&gt;Kháng Glacio&lt;/color&gt; cao hơn.</t>
         </is>
       </c>
     </row>
@@ -31110,7 +31111,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>[Kháng cự]: Kẻ địch này có &lt;color=Fire&gt;Fusion RES&lt;/color&gt; cao hơn.</t>
+          <t>[Kháng cự]: Kẻ địch này có &lt;color=Fire&gt;Kháng Fusion&lt;/color&gt; cao hơn.</t>
         </is>
       </c>
     </row>
@@ -31175,7 +31176,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>[Kháng]: Kẻ địch này có &lt;color=Thunder&gt;Electro RES&lt;/color&gt; cao hơn.</t>
+          <t>[Kháng]: Kẻ địch này có &lt;color=Thunder&gt;Kháng Electro&lt;/color&gt; cao hơn.</t>
         </is>
       </c>
     </row>
@@ -31240,7 +31241,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Aero RES&lt;/color&gt; cao hơn.</t>
+          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Kháng Aero&lt;/color&gt; cao hơn.</t>
         </is>
       </c>
     </row>
@@ -31305,7 +31306,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>[Kháng Cự]: Kẻ địch này có &lt;color=Light&gt;Spectro RES&lt;/color&gt; cao hơn.</t>
+          <t>[Kháng Cự]: Kẻ địch này có &lt;color=Light&gt;Kháng Spectro&lt;/color&gt; cao hơn.</t>
         </is>
       </c>
     </row>
@@ -31370,7 +31371,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>[Kháng cự]: Kẻ địch này có &lt;color=Dark&gt;Havoc RES&lt;/color&gt; cao hơn.</t>
+          <t>[Kháng cự]: Kẻ địch này có &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; cao hơn.</t>
         </is>
       </c>
     </row>
@@ -31435,7 +31436,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>[Kháng]: Kẻ địch này có &lt;color=Wind&gt;Aero RES&lt;/color&gt; và &lt;color=Ice&gt;Glacio RES&lt;/color&gt; cao hơn.</t>
+          <t>[Kháng]: Kẻ địch này có &lt;color=Wind&gt;Kháng Aero&lt;/color&gt; và &lt;color=Ice&gt;Kháng Glacio&lt;/color&gt; cao hơn.</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31501,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>[Kháng]: Kẻ địch này có &lt;color=Thunder&gt;Electro RES&lt;/color&gt; và &lt;color=Dark&gt;Havoc RES&lt;/color&gt; cao hơn.</t>
+          <t>[Kháng]: Kẻ địch này có &lt;color=Thunder&gt;Kháng Electro&lt;/color&gt; và &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; cao hơn.</t>
         </is>
       </c>
     </row>
@@ -31565,7 +31566,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Data thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa hàng Simulation Training.</t>
+          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Dữ Liệu thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa Hàng Huấn Luyện Mô Phỏng.</t>
         </is>
       </c>
     </row>
@@ -31630,7 +31631,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Data thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa hàng Simulation Training.</t>
+          <t>Thiết bị Âm Thanh Mô Phỏng do Tòa án Savantae để lại có thể mô phỏng kẻ địch mạnh. Bộ Dữ Liệu thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa Hàng Huấn Luyện Mô Phỏng.</t>
         </is>
       </c>
     </row>
@@ -31695,7 +31696,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Một Terminal đặc biệt do Fisalias và Hội phát triển, có khả năng mô phỏng những kẻ địch mạnh mẽ. Đồng Xu Trial thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa hàng Trial.</t>
+          <t>Một Thiết bị đầu cuối đặc biệt do Fisalias và Hội phát triển, có khả năng mô phỏng những kẻ địch mạnh mẽ. Đồng Xu Thử Thách thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa Hàng Thử Thách.</t>
         </is>
       </c>
     </row>
@@ -31763,10 +31764,10 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>[Kháng]: Kẻ địch này có &lt;color=Thunder&gt;Electro RES&lt;/color&gt; cao hơn.
-[Thunder]: Sau 3 phút giao tranh, Tấn Công của Tempest Mephis tăng 50% mỗi 10 giây, không giới hạn cộng dồn.
-[Lôi Điện]: Khi đòn tấn công của Tempest Mephis trúng mục tiêu, Tấn Công của nó tăng 10% và Phòng Ngự giảm 10% trong 12 giây, không giới hạn cộng dồn.
-[Sốc Điện]: Trong vòng 8 giây sau Phản Đòn, tốc độ deplete Vibration Strength của đòn tấn công của Resonator tăng 25%, tối đa cộng dồn 8 lần.</t>
+          <t>[Kháng]: Kẻ địch này có &lt;color=Thunder&gt;Kháng Electro&lt;/color&gt; cao hơn.
+[Sấm Sét]: Sau 3 phút giao tranh, ATK của Tempest Mephis tăng 50% mỗi 10 giây, không giới hạn cộng dồn.
+[Lôi Điện]: Khi đòn tấn công của Tempest Mephis trúng mục tiêu, ATK của nó tăng 10% và Phòng Ngự giảm 10% trong 12 giây, không giới hạn cộng dồn.
+[Sốc Điện]: Trong vòng 8 giây sau Phản Đòn, tốc độ tiêu hao Sức Rung của đòn tấn công của Resonator tăng 25%, tối đa cộng dồn 8 lần.</t>
         </is>
       </c>
     </row>
@@ -31834,10 +31835,10 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>[Kháng]: Kẻ địch này có &lt;color=Thunder&gt;Electro RES&lt;/color&gt; cao hơn.
-[Thunder]: Sau 3 phút giao tranh, Tấn Công của Tempest Mephis tăng 50% mỗi 10 giây, không giới hạn cộng dồn.
-[Lôi Điện]: Khi đòn tấn công của Tempest Mephis trúng mục tiêu, Tấn Công của nó tăng 10% và Phòng Ngự giảm 10% trong 12 giây, không giới hạn cộng dồn.
-[Sốc Điện]: Trong vòng 8 giây sau Phản Đòn, tốc độ deplete Vibration Strength của đòn tấn công của Resonator tăng 25%, tối đa cộng dồn 8 lần.</t>
+          <t>[Kháng]: Kẻ địch này có &lt;color=Thunder&gt;Kháng Electro&lt;/color&gt; cao hơn.
+[Sấm Sét]: Sau 3 phút giao tranh, ATK của Tempest Mephis tăng 50% mỗi 10 giây, không giới hạn cộng dồn.
+[Lôi Điện]: Khi đòn tấn công của Tempest Mephis trúng mục tiêu, ATK của nó tăng 10% và Phòng Ngự giảm 10% trong 12 giây, không giới hạn cộng dồn.
+[Sốc Điện]: Trong vòng 8 giây sau Phản Đòn, tốc độ tiêu hao Sức Rung của đòn tấn công của Resonator tăng 25%, tối đa cộng dồn 8 lần.</t>
         </is>
       </c>
     </row>
@@ -31905,8 +31906,8 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>[Kháng]: Kẻ địch này có &lt;color=Dark&gt;Havoc RES&lt;/color&gt; cao hơn.
-[Fierce Cry]: 3 phút sau khi trận chiến bắt đầu, Impermanence Heron sẽ tăng Tấn Công thêm 50% mỗi 10 giây, không giới hạn số lần cộng dồn.
+          <t>[Kháng]: Kẻ địch này có &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; cao hơn.
+[Fierce Cry]: 3 phút sau khi trận chiến bắt đầu, Impermanence Heron sẽ tăng ATK thêm 50% mỗi 10 giây, không giới hạn số lần cộng dồn.
 [Bone Crushing]: Khi bị tấn công bởi Impermanence Heron, Phòng Ngự của Resonator sẽ giảm 10% trong 15 giây, không giới hạn số lần cộng dồn.
 [Startling Bow]: Khi kỹ năng Echo Counter phản đòn thành công một kỹ năng đặc biệt, đòn tấn công tiếp theo trong vòng 5 giây sẽ làm giảm thêm 30% Vibration Strength của kẻ địch.</t>
         </is>
@@ -31976,8 +31977,8 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>[Kháng]: Kẻ địch này có &lt;color=Dark&gt;Havoc RES&lt;/color&gt; cao hơn.
-[Fierce Cry]: 3 phút sau khi trận chiến bắt đầu, Impermanence Heron sẽ tăng Tấn Công thêm 50% mỗi 10 giây, không giới hạn số lần cộng dồn.
+          <t>[Kháng]: Kẻ địch này có &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; cao hơn.
+[Fierce Cry]: 3 phút sau khi trận chiến bắt đầu, Impermanence Heron sẽ tăng ATK thêm 50% mỗi 10 giây, không giới hạn số lần cộng dồn.
 [Bone Crushing]: Khi bị tấn công bởi Impermanence Heron, Phòng Ngự của Resonator sẽ giảm 10% trong 15 giây, không giới hạn số lần cộng dồn.
 [Startling Bow]: Khi kỹ năng Echo Counter phản đòn thành công một kỹ năng đặc biệt, đòn tấn công tiếp theo trong vòng 5 giây sẽ làm giảm thêm 30% Vibration Strength của kẻ địch.</t>
         </is>
@@ -32047,10 +32048,10 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>[Kháng Cự]: Kẻ địch này có &lt;color=Light&gt;Spectro RES&lt;/color&gt; cao hơn.
-[Lạnh Xương]: Sau 3 phút giao tranh, Mourning Aix sẽ tăng Tấn Công 50% mỗi 10 giây, không giới hạn chồng.
-[Panic]: Trong trận chiến, Resonators bị thương sẽ tiêu hao thêm 10 STA khi Dodge.
-[Rình Rập]: Sau mỗi 5 lần Phản Đòn, đòn tấn công tiếp theo sẽ làm giảm thêm 40% Vibration Strength của kẻ địch. Bộ đếm này sẽ reset khi bị tấn công.</t>
+          <t>[Kháng Cự]: Kẻ địch này có &lt;color=Light&gt;Kháng Spectro&lt;/color&gt; cao hơn.
+[Lạnh Xương]: Sau 3 phút giao tranh, Mourning Aix sẽ tăng ATK 50% mỗi 10 giây, không giới hạn chồng.
+[Hoảng Loạn]: Trong trận chiến, Resonator bị thương sẽ tiêu hao thêm 10 STA khi Né.
+[Rình Rập]: Sau mỗi 5 lần Phản Đòn, đòn tấn công tiếp theo sẽ làm giảm thêm 40% Sức Rung của kẻ địch. Bộ đếm này sẽ reset khi bị tấn công.</t>
         </is>
       </c>
     </row>
@@ -32118,10 +32119,10 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>[Kháng Cự]: Kẻ địch này có &lt;color=Light&gt;Spectro RES&lt;/color&gt; cao hơn.
-[Lạnh Xương]: Sau 3 phút giao tranh, Mourning Aix sẽ tăng Tấn Công 50% mỗi 10 giây, không giới hạn chồng.
-[Panic]: Trong trận chiến, Resonators bị thương sẽ tiêu hao thêm 10 STA khi Dodge.
-[Rình Rập]: Sau mỗi 5 lần Phản Đòn, đòn tấn công tiếp theo sẽ làm giảm thêm 40% Vibration Strength của kẻ địch. Bộ đếm này sẽ reset khi bị tấn công.</t>
+          <t>[Kháng Cự]: Kẻ địch này có &lt;color=Light&gt;Kháng Spectro&lt;/color&gt; cao hơn.
+[Lạnh Xương]: Sau 3 phút giao tranh, Mourning Aix sẽ tăng ATK 50% mỗi 10 giây, không giới hạn chồng.
+[Hoảng Loạn]: Trong trận chiến, Resonator bị thương sẽ tiêu hao thêm 10 STA khi Né.
+[Rình Rập]: Sau mỗi 5 lần Phản Đòn, đòn tấn công tiếp theo sẽ làm giảm thêm 40% Sức Rung của kẻ địch. Bộ đếm này sẽ reset khi bị tấn công.</t>
         </is>
       </c>
     </row>
@@ -32189,10 +32190,10 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Aero RES&lt;/color&gt; cao hơn.
-[Tiếng Gầm Chiến]: Sau 3 phút kể từ khi trận chiến bắt đầu, Feilian Beringal sẽ tăng 50% Tấn Công mỗi 10 giây, không giới hạn cộng dồn.
-[Hàng Ngũ]: Nếu Resonator ở trạng thái HP đầy, Intro Skill sẽ tăng Tỷ Lệ deplete Vibration Strength của kẻ địch thêm 5% khi trúng đòn trong 15 giây, tối đa 20 lần cộng dồn.
-[Phản Bội]: Sau mỗi 10 lần Dodge Counter, đòn tấn công tiếp theo sẽ tiêu hao thêm 30% Vibration Strength của kẻ địch. Bộ đếm này sẽ reset khi bị tấn công.</t>
+          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Kháng Aero&lt;/color&gt; cao hơn.
+[Tiếng Gầm Chiến]: Sau 3 phút kể từ khi trận chiến bắt đầu, Feilian Beringal sẽ tăng 50% ATK mỗi 10 giây, không giới hạn cộng dồn.
+[Hàng Ngũ]: Nếu Resonator ở trạng thái HP đầy, Kỹ Năng Khởi Động sẽ tăng Tỷ Lệ Giảm Sức Rung của kẻ địch thêm 5% khi trúng đòn trong 15 giây, tối đa 20 lần cộng dồn.
+[Phản Bội]: Sau mỗi 10 lần Né Phản Đòn, đòn tấn công tiếp theo sẽ tiêu hao thêm 30% Sức Rung của kẻ địch. Bộ đếm này sẽ reset khi bị tấn công.</t>
         </is>
       </c>
     </row>
@@ -32260,10 +32261,10 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Aero RES&lt;/color&gt; cao hơn.
-[Tiếng Gầm Chiến]: Sau 3 phút kể từ khi trận chiến bắt đầu, Feilian Beringal sẽ tăng 50% Tấn Công mỗi 10 giây, không giới hạn cộng dồn.
-[Hàng Ngũ]: Nếu Resonator ở trạng thái HP đầy, Intro Skill sẽ tăng Tỷ Lệ deplete Vibration Strength của kẻ địch thêm 5% khi trúng đòn trong 15 giây, tối đa 20 lần cộng dồn.
-[Phản Bội]: Sau mỗi 10 lần Dodge Counter, đòn tấn công tiếp theo sẽ tiêu hao thêm 30% Vibration Strength của kẻ địch. Bộ đếm này sẽ reset khi bị tấn công.</t>
+          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Kháng Aero&lt;/color&gt; cao hơn.
+[Tiếng Gầm Chiến]: Sau 3 phút kể từ khi trận chiến bắt đầu, Feilian Beringal sẽ tăng 50% ATK mỗi 10 giây, không giới hạn cộng dồn.
+[Hàng Ngũ]: Nếu Resonator ở trạng thái HP đầy, Kỹ Năng Khởi Động sẽ tăng Tỷ Lệ Giảm Sức Rung của kẻ địch thêm 5% khi trúng đòn trong 15 giây, tối đa 20 lần cộng dồn.
+[Phản Bội]: Sau mỗi 10 lần Né Phản Đòn, đòn tấn công tiếp theo sẽ tiêu hao thêm 30% Sức Rung của kẻ địch. Bộ đếm này sẽ reset khi bị tấn công.</t>
         </is>
       </c>
     </row>
@@ -32329,8 +32330,8 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>[Kháng cự]: Kẻ địch này có &lt;color=Dark&gt;Havoc RES&lt;/color&gt; cao hơn.
-[Nhiệt Huyết] Dodge Counter thành công sẽ tăng Crit. DMG của Resonator lên 15% trong 15 giây, tối đa 4 lần.</t>
+          <t>[Kháng cự]: Kẻ địch này có &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; cao hơn.
+[Nhiệt Huyết] Phản đòn né thành công sẽ tăng Crit. DMG của Resonator lên 15% trong 15 giây, tối đa 4 lần.</t>
         </is>
       </c>
     </row>
@@ -32395,7 +32396,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>["Hăng Hái" Dodge Counter thành công tăng Crit. DMG của Resonator thêm 15% trong 15 giây, tối đa 4 lần cộng dồn.</t>
+          <t>["Hăng Hái" Dodge Counter Tránh thành công tăng Crit. DMG của Resonator thêm 15% trong 15 giây, tối đa 4 lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -32460,7 +32461,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>["Hăng Hái" Dodge Counter thành công tăng Crit. DMG của Resonator thêm 15% trong 15 giây, tối đa 4 lần cộng dồn.</t>
+          <t>["Hăng Hái" Dodge Counter Tránh thành công tăng Crit. DMG của Resonator thêm 15% trong 15 giây, tối đa 4 lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -32527,9 +32528,9 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>[Kháng cự]: Kẻ địch này có &lt;color=Dark&gt;Havoc RES&lt;/color&gt; cao hơn.
-[Nhiệt Huyết] Dodge Counter thành công sẽ tăng Crit. DMG của Resonator lên 15% trong 15 giây, tối đa 4 lần.
-[Cuồng Nộ] Dodge Counter gây thêm 100% Sát Thương và giảm thêm 5% Vibration Strength.</t>
+          <t>[Kháng cự]: Kẻ địch này có &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; cao hơn.
+[Nhiệt Huyết] Phản đòn né thành công sẽ tăng Crit. DMG của Resonator lên 15% trong 15 giây, tối đa 4 lần.
+[Cuồng Nộ] Phản đòn né gây thêm 100% Sát Thương và giảm thêm 5% Độ rung của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -32595,8 +32596,8 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>["Hăng Hái" Dodge Counter thành công tăng Crit. DMG của Resonator thêm 15% trong 15 giây, tối đa 4 lần cộng dồn.
-["Mãnh Liệt" Dodge Counter gây thêm 100% sát thương và giảm thêm 5% Vibration Strength của kẻ địch.</t>
+          <t>["Hăng Hái" Dodge Counter Tránh thành công tăng Crit. DMG của Resonator thêm 15% trong 15 giây, tối đa 4 lần cộng dồn.
+["Mãnh Liệt" Dodge Counter Tránh gây thêm 100% DMG và giảm thêm 5% Độ Mạnh Rung của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -32662,8 +32663,8 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>["Hăng Hái" Dodge Counter thành công tăng Crit. DMG của Resonator thêm 15% trong 15 giây, tối đa 4 lần cộng dồn.
-["Mãnh Liệt" Dodge Counter gây thêm 100% sát thương và giảm thêm 5% Vibration Strength của kẻ địch.</t>
+          <t>["Hăng Hái" Dodge Counter Tránh thành công tăng Crit. DMG của Resonator thêm 15% trong 15 giây, tối đa 4 lần cộng dồn.
+["Mãnh Liệt" Dodge Counter Tránh gây thêm 100% DMG và giảm thêm 5% Độ Mạnh Rung của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -32730,9 +32731,9 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>[Kháng cự]: Kẻ địch này có &lt;color=Fire&gt;Fusion RES&lt;/color&gt; cao hơn.
-[Hỏa Tai] Intro Skill tăng Tấn Công của tất cả Resonators trong đội lên 10% trong 15 giây, tối đa 3 lần.
-[Thần Tốc] Increase Tấn Công của Resonators lên 20% khi HP trên 80%.</t>
+          <t>[Kháng cự]: Kẻ địch này có &lt;color=Fire&gt;Kháng Fusion&lt;/color&gt; cao hơn.
+[Hỏa Tai] Kỹ Năng Khởi Động tăng ATK của tất cả Resonator trong đội lên 10% trong 15 giây, tối đa 3 lần.
+[Thần Tốc] Tăng ATK của Resonator lên 20% khi HP trên 80%.</t>
         </is>
       </c>
     </row>
@@ -32799,9 +32800,9 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>[Kháng]: Kẻ địch này có &lt;color=Light&gt;Spectro RES&lt;/color&gt; cao hơn.
-[Chính Xác]: Dodge thành công sẽ nhận được 1 điểm Hoverpoint trong 3 giây. Khi đạt 3 điểm, tất cả Hoverpoint sẽ được xóa để kích hoạt Supercompute trong 20 giây. [Supercompute]: Tấn Công của Resonators tăng 30%, đồng thời phục hồi 5 STA mỗi giây.
-[Sụp Đổ]: Sau 3 phút giao tranh, Tấn Công của kẻ địch tăng 30% mỗi 10 giây, không giới hạn số lần cộng dồn. Tấn Công của Resonators cũng tăng 10% mỗi 10 giây, tối đa 100%. Tất cả Resonators trong đội mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
+          <t>[Kháng]: Kẻ địch này có &lt;color=Light&gt;Kháng Spectro&lt;/color&gt; cao hơn.
+[Chính Xác]: Né thành công sẽ nhận được 1 điểm Hoverpoint trong 3 giây. Khi đạt 3 điểm, tất cả Hoverpoint sẽ được xóa để kích hoạt Supercompute trong 20 giây. [Supercompute]: ATK của Resonator tăng 30%, đồng thời phục hồi 5 STA mỗi giây.
+[Sụp Đổ]: Sau 3 phút giao tranh, ATK của kẻ địch tăng 30% mỗi 10 giây, không giới hạn số lần cộng dồn. ATK của Resonator cũng tăng 10% mỗi 10 giây, tối đa 100%. Tất cả Resonator trong đội mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
         </is>
       </c>
     </row>
@@ -32869,10 +32870,10 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>[Kháng Cự]: Kẻ địch này có &lt;color=Ice&gt;Glacio RES&lt;/color&gt; cao hơn.
+          <t>[Kháng Cự]: Kẻ địch này có &lt;color=Ice&gt;Kháng Glacio&lt;/color&gt; cao hơn.
 [Hàng Rào]: Sentry Construct trong tư thế phòng thủ sẽ không tạo ra điểm Treo.
-[Rơi Light]: Khi Sentry Construct ở trên không, mỗi lần chịu sát thương sẽ làm giảm thêm 1% Vibration Strength. Hiệu ứng này kích hoạt mỗi 0,5 giây. Nếu chịu sát thương khi đang bị Spectro Frazzle, Vibration Strength giảm thêm 2%, kích hoạt mỗi giây.
-[Fall]: Sau 3 phút giao tranh, Tấn Công của kẻ địch tăng 30% mỗi 10 giây, không giới hạn chồng. Tấn Công của Resonators tăng 10% mỗi 10 giây, tối đa 100%. Tất cả Resonators trong đội mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
+[Rơi Ánh Sáng]: Khi Sentry Construct ở trên không, mỗi lần chịu sát thương sẽ làm giảm thêm 1% Sức Rung. Hiệu ứng này kích hoạt mỗi 0,5 giây. Nếu chịu sát thương khi đang bị Spectro Frazzle, Sức Rung giảm thêm 2%, kích hoạt mỗi giây.
+[Sụp Đổ]: Sau 3 phút giao tranh, ATK của kẻ địch tăng 30% mỗi 10 giây, không giới hạn chồng. ATK của Resonator tăng 10% mỗi 10 giây, tối đa 100%. Tất cả Resonator trong đội mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
         </is>
       </c>
     </row>
@@ -32938,8 +32939,8 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>[Kháng Cự]: Kẻ địch này có &lt;color=Ice&gt;Glacio RES&lt;/color&gt; cao hơn.
-[Hàng Rào]: Sentry Construct trong tư thế phòng thủ sẽ không tạo ra điểm Treo.</t>
+          <t>[Kháng Cự]: This enemy has a higher &lt;color=Ice&gt;Glacio RES&lt;/color&gt;.
+[Barricade]: No Grapple point will be generated when Sentry Construct is in defense stance.</t>
         </is>
       </c>
     </row>
@@ -33005,8 +33006,8 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>[Kháng]: Kẻ địch này có &lt;color=Dark&gt;Havoc RES&lt;/color&gt; cao hơn.
-[False Face]: Sau khi sử dụng kỹ năng Hecate's Echo, Resonator chủ động sẽ chịu ít sát thương hơn và có khả năng chống gián đoạn tăng trong 3 giây. Cooldown chiêu của kỹ năng Hecate's Echo giảm 30%.</t>
+          <t>[Kháng]: Kẻ địch này có &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; cao hơn.
+[False Face]: Sau khi sử dụng kỹ năng Hecate's Echo, Resonator chủ động sẽ chịu ít DMG hơn và có khả năng chống gián đoạn tăng trong 3 giây. Thời gian hồi chiêu của kỹ năng Hecate's Echo giảm 30%.</t>
         </is>
       </c>
     </row>
@@ -33073,9 +33074,9 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>[Kháng]: Kẻ địch này có &lt;color=Dark&gt;Havoc RES&lt;/color&gt; cao hơn.
-[False Face]: Sau khi sử dụng kỹ năng Hecate's Echo, Resonators chủ động sẽ chịu ít sát thương hơn và có khả năng chống gián đoạn tăng trong 3 giây. Cooldown chiêu của kỹ năng Hecate's Echo giảm 30%.
-[Death's Dance]: 3 phút sau khi trận chiến bắt đầu, Tấn Công của Resonators sẽ tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn số lần cộng dồn. Mọi Resonators trong đội sẽ mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
+          <t>[Kháng]: Kẻ địch này có &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; cao hơn.
+[False Face]: Sau khi sử dụng kỹ năng Hecate's Echo, Resonator chủ động sẽ chịu ít DMG hơn và có khả năng chống gián đoạn tăng trong 3 giây. Thời gian hồi chiêu của kỹ năng Hecate's Echo giảm 30%.
+[Death's Dance]: 3 phút sau khi trận chiến bắt đầu, ATK của Resonator sẽ tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn số lần cộng dồn. Mọi Resonator trong đội sẽ mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
         </is>
       </c>
     </row>
@@ -33141,8 +33142,8 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>[Kháng cự]: Kẻ địch này có &lt;color=Fire&gt;Fusion RES&lt;/color&gt; cao hơn.
-[Hợp Âm Ảo]: Khi biến hình thành Lorelei, miễn nhiễm với Sát Thương từ Dragon of Dirge, tăng Fusion RES của tất cả Resonators trong đội lên 20% trong 15 giây. Bị Dragon of Dirge tấn công trong quá trình biến hình sẽ giảm Độ rung của nó.</t>
+          <t>[Kháng cự]: Kẻ địch này có &lt;color=Fire&gt;Kháng Fusion&lt;/color&gt; cao hơn.
+[Hợp Âm Ảo]: Khi biến hình thành Lorelei, miễn nhiễm với Sát Thương từ Dragon of Dirge, tăng Kháng Fusion của tất cả Resonator trong đội lên 20% trong 15 giây. Bị Dragon of Dirge tấn công trong quá trình biến hình sẽ giảm Độ rung của nó.</t>
         </is>
       </c>
     </row>
@@ -33210,10 +33211,10 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>[Kháng cự]: Kẻ địch này có &lt;color=Fire&gt;Fusion RES&lt;/color&gt; cao hơn.
-[Hợp Âm Ảo]: Khi biến hình thành Lorelei, miễn nhiễm với Sát Thương từ Dragon of Dirge, tăng Fusion RES của tất cả Resonators trong đội lên 20% trong 15 giây. Bị Dragon of Dirge tấn công trong quá trình biến hình sẽ giảm Độ rung của nó.
-[Sụp Đổ]: Sau 3 phút kể từ khi trận chiến bắt đầu, Tấn Công của Resonators sẽ tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn cộng dồn. Tất cả Resonators trong đội sẽ mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.
-[Đôi Cánh Xòe Rộng] Mỗi lần Dodge thành công sẽ phục hồi một lượng STA nhất định cho Resonators và tăng Tấn Công lên 10% trong 5 giây, tối đa 5 lần.</t>
+          <t>[Kháng cự]: Kẻ địch này có &lt;color=Fire&gt;Kháng Fusion&lt;/color&gt; cao hơn.
+[Hợp Âm Ảo]: Khi biến hình thành Lorelei, miễn nhiễm với Sát Thương từ Dragon of Dirge, tăng Kháng Fusion của tất cả Resonator trong đội lên 20% trong 15 giây. Bị Dragon of Dirge tấn công trong quá trình biến hình sẽ giảm Độ rung của nó.
+[Sụp Đổ]: Sau 3 phút kể từ khi trận chiến bắt đầu, ATK của Resonator sẽ tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn cộng dồn. Tất cả Resonator trong đội sẽ mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.
+[Đôi Cánh Xòe Rộng] Mỗi lần né thành công sẽ phục hồi một lượng STA nhất định cho Resonator và tăng ATK lên 10% trong 5 giây, tối đa 5 lần.</t>
         </is>
       </c>
     </row>
@@ -33279,8 +33280,8 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Aero RES&lt;/color&gt; cao hơn.
-[Gợn Sóng]: Dodge thành công sẽ hồi một lượng STA nhất định và tăng 10% Crit. DMG trong 5 giây, tối đa 5 lần cộng dồn.</t>
+          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Kháng Aero&lt;/color&gt; cao hơn.
+[Gợn Sóng]: Né thành công sẽ hồi một lượng STA nhất định và tăng 10% Crit. DMG trong 5 giây, tối đa 5 lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -33348,10 +33349,10 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Aero RES&lt;/color&gt; cao hơn.
-[Gợn Sóng]: Dodge thành công sẽ hồi một lượng STA nhất định và tăng 10% Crit. DMG trong 5 giây, tối đa 5 lần cộng dồn.
-[Sắc Hồ]: Khi kẻ địch chịu Spectro DMG Frazzle, Phòng Ngự của tất cả Resonators trong đội sẽ tăng 2% trong 10 giây, tối đa 15 lần cộng dồn.
-[Điệu Vũ Tử Thần]: Sau 3 phút kể từ khi trận chiến bắt đầu, Tấn Công của Resonators sẽ tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương Nhận Vào cũng sẽ tăng 10% mỗi 10 giây, không giới hạn cộng dồn. Mọi Resonators trong đội sẽ mất 10% HP tối đa mỗi 2 giây cho đến khi HP còn dưới 20%.</t>
+          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Kháng Aero&lt;/color&gt; cao hơn.
+[Gợn Sóng]: Né thành công sẽ hồi một lượng STA nhất định và tăng 10% Crit. DMG trong 5 giây, tối đa 5 lần cộng dồn.
+[Sắc Hồ]: Khi kẻ địch chịu Sát Thương Spectro Frazzle, Phòng Ngự của tất cả Resonator trong đội sẽ tăng 2% trong 10 giây, tối đa 15 lần cộng dồn.
+[Điệu Vũ Tử Thần]: Sau 3 phút kể từ khi trận chiến bắt đầu, ATK của Resonator sẽ tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương Nhận Vào cũng sẽ tăng 10% mỗi 10 giây, không giới hạn cộng dồn. Mọi Resonator trong đội sẽ mất 10% HP tối đa mỗi 2 giây cho đến khi HP còn dưới 20%.</t>
         </is>
       </c>
     </row>
